--- a/result_half_test.xlsx
+++ b/result_half_test.xlsx
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>99.33</v>
       </c>
       <c r="C2" t="n">
         <v>46.66</v>
       </c>
       <c r="D2" t="n">
-        <v>53.34</v>
+        <v>52.67</v>
       </c>
       <c r="E2" t="n">
-        <v>114.32</v>
+        <v>112.89</v>
       </c>
     </row>
     <row r="3">
@@ -554,16 +554,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>72.34</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>76.66</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>-4.32</v>
       </c>
       <c r="E3" t="n">
-        <v>14.29</v>
+        <v>-5.64</v>
       </c>
     </row>
     <row r="4">
@@ -573,16 +573,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>86.66</v>
       </c>
       <c r="D4" t="n">
-        <v>-10</v>
+        <v>13.34</v>
       </c>
       <c r="E4" t="n">
-        <v>-20</v>
+        <v>15.39</v>
       </c>
     </row>
     <row r="5">
@@ -592,16 +592,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -611,16 +611,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>72.5</v>
+        <v>87.67</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>54.16</v>
+        <v>65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18.34</v>
+        <v>22.67</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>33.85</v>
+        <v>34.88</v>
       </c>
     </row>
   </sheetData>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="6">
@@ -1054,13 +1054,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1436,13 +1436,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5">
@@ -1542,13 +1542,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="6">
@@ -1664,13 +1664,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -1802,13 +1802,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-100</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="5">
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="6">
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -2062,13 +2062,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="6">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">
@@ -2254,17 +2254,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2274,26 +2274,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2302,7 +2302,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2322,13 +2322,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2376,17 +2376,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2396,26 +2396,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2424,7 +2424,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2498,17 +2498,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2518,26 +2518,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2566,13 +2566,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2620,17 +2620,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2640,26 +2640,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2688,13 +2688,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2742,17 +2742,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2762,26 +2762,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2810,13 +2810,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2864,17 +2864,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2884,26 +2884,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2986,17 +2986,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3006,26 +3006,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3034,7 +3034,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3054,13 +3054,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3108,17 +3108,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3128,26 +3128,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3156,7 +3156,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3352,17 +3352,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3372,26 +3372,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3400,7 +3400,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3420,13 +3420,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3474,17 +3474,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3494,26 +3494,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3522,7 +3522,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3596,65 +3596,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -3664,13 +3664,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -3718,65 +3718,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -3786,13 +3786,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -3840,65 +3840,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -3908,13 +3908,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -3962,65 +3962,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4030,13 +4030,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4084,14 +4084,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -4100,49 +4100,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4206,65 +4206,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4328,65 +4328,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4396,13 +4396,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4450,65 +4450,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4518,13 +4518,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4694,65 +4694,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4762,13 +4762,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4816,65 +4816,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4884,13 +4884,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
     </row>
   </sheetData>
@@ -4980,17 +4980,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="C3" t="n">
         <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>66.7</v>
+        <v>63.37</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 66.7, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5084,13 +5084,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>100</v>
+        <v>99.33</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>46.66</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>53.34</v>
+        <v>52.67</v>
       </c>
     </row>
   </sheetData>
@@ -5180,22 +5180,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>33.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>66.7, 66.7, 66.7, 66.7, 66.7, 66.7, 66.7, 66.7, 66.7, 66.7</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3</t>
         </is>
       </c>
     </row>
@@ -5206,17 +5206,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-100</v>
+        <v>-85</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>0.0, 50.0, 0.0, 0.0, 50.0, 0.0, 0.0, 50.0, 0.0, 0.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5232,17 +5232,17 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>50.0, 100.0, 100.0, 100.0, 100.0, 50.0, 100.0, 50.0, 50.0, 100.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5284,13 +5284,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>80</v>
+        <v>72.34</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>70</v>
+        <v>76.66</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10</v>
+        <v>-4.32</v>
       </c>
     </row>
   </sheetData>
@@ -5350,26 +5350,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put CD and Cellphone in the drawer</t>
+          <t>Put the Cellphone and pencil on the sh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
     </row>
@@ -5380,55 +5380,55 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put the vase into the garbagecan and b</t>
+          <t>Turn off the lightswitch</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turn off the lightswitch</t>
+          <t>Turn off the lightswitch and open the</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5458,17 +5458,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5484,13 +5484,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>50</v>
+        <v>86.66</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-10</v>
+        <v>13.34</v>
       </c>
     </row>
   </sheetData>
@@ -5550,43 +5550,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Put ScrubBrush on the bathtub</t>
+          <t>Put Plunger in the cabinet and Put the</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 50.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Put papertowelroll on the countertop</t>
+          <t>Put ScrubBrush on the bathtub</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -5595,28 +5595,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Put spraybottle on the countertop</t>
+          <t>Put papertowelroll on the countertop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5628,26 +5628,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Put the cloth and handtowel into the s</t>
+          <t>Put the dishsponge in the sinkbasin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
     </row>
@@ -5658,17 +5658,17 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>100</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5684,13 +5684,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -6124,13 +6124,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="C3" t="n">
         <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>66.7</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="4">

--- a/result_half_test.xlsx
+++ b/result_half_test.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -499,6 +499,10 @@
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +531,26 @@
           <t>개선율 (%)</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>개선율 Exec (%)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -535,16 +559,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99.33</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
         <v>46.66</v>
       </c>
       <c r="D2" t="n">
-        <v>52.67</v>
+        <v>53.34</v>
       </c>
       <c r="E2" t="n">
-        <v>112.89</v>
+        <v>114.32</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -554,16 +590,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.34</v>
+        <v>71.34</v>
       </c>
       <c r="C3" t="n">
         <v>76.66</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.32</v>
+        <v>-5.32</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.64</v>
+        <v>-6.94</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -584,6 +632,18 @@
       <c r="E4" t="n">
         <v>15.39</v>
       </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,16 +652,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C5" t="n">
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -611,16 +683,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>87.67</v>
+        <v>86.84</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>65</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>22.67</v>
+        <v>21.84</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34.88</v>
+        <v>33.6</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -634,13 +718,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +751,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -680,6 +782,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -696,6 +807,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -712,6 +832,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -728,6 +857,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -742,6 +880,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -756,13 +903,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,6 +936,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -802,6 +967,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -818,6 +992,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -834,6 +1017,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -850,6 +1042,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -864,6 +1065,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -878,13 +1088,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -908,6 +1121,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -924,6 +1152,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -940,6 +1177,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -956,6 +1202,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -964,13 +1219,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -986,6 +1250,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1000,13 +1273,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1030,6 +1306,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1046,6 +1337,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1062,6 +1362,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1078,6 +1387,15 @@
       <c r="D4" t="n">
         <v>-50</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1086,12 +1404,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1108,6 +1435,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1122,13 +1458,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1152,6 +1491,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1168,6 +1522,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1184,6 +1547,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1200,6 +1572,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1216,6 +1597,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1230,6 +1620,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1244,13 +1643,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1274,6 +1676,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1290,6 +1707,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1306,6 +1732,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1322,6 +1757,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1330,12 +1774,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1352,6 +1805,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1366,13 +1828,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1396,6 +1861,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1412,6 +1892,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1428,6 +1917,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1436,13 +1934,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-50</v>
+        <v>-100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1460,6 +1967,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1474,6 +1990,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1488,13 +2013,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1518,6 +2046,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1534,6 +2077,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1550,6 +2102,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1566,6 +2127,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1574,13 +2144,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1596,6 +2175,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1610,13 +2198,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1640,6 +2231,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1656,6 +2262,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1672,6 +2287,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1688,6 +2312,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1704,6 +2337,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1718,6 +2360,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1732,13 +2383,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1762,6 +2416,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1778,6 +2447,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1794,6 +2472,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1802,13 +2489,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-50</v>
+        <v>-100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1826,6 +2522,15 @@
       <c r="D5" t="n">
         <v>-50</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1840,6 +2545,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1854,13 +2568,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1884,6 +2601,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1900,6 +2632,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1916,6 +2657,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1932,6 +2682,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1948,6 +2707,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1962,6 +2730,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1976,13 +2753,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2006,6 +2786,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2022,6 +2817,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2038,6 +2842,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2054,6 +2867,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2062,13 +2884,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>-50</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2084,6 +2915,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2098,13 +2938,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2128,6 +2971,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2144,6 +3002,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2160,6 +3027,15 @@
       <c r="D3" t="n">
         <v>33.4</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2176,6 +3052,15 @@
       <c r="D4" t="n">
         <v>-100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2192,6 +3077,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2206,6 +3100,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2220,13 +3123,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2250,6 +3156,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2266,6 +3187,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2282,6 +3212,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2298,6 +3237,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2314,6 +3262,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2328,6 +3285,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2342,13 +3308,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2372,6 +3341,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2388,6 +3372,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2404,6 +3397,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2420,6 +3422,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2436,6 +3447,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2450,6 +3470,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2464,13 +3493,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2494,6 +3526,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2510,6 +3557,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2526,6 +3582,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2542,6 +3607,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2558,6 +3632,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2572,6 +3655,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2586,13 +3678,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2616,6 +3711,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2632,6 +3742,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2648,6 +3767,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2664,6 +3792,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2680,6 +3817,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2694,6 +3840,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2708,13 +3863,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2738,6 +3896,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2754,6 +3927,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2770,6 +3952,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2786,6 +3977,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2802,6 +4002,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2816,6 +4025,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2830,13 +4048,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2860,6 +4081,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2876,6 +4112,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2892,6 +4137,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2908,6 +4162,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2924,6 +4187,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2938,6 +4210,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2952,13 +4233,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2982,6 +4266,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2998,6 +4297,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3014,6 +4322,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3030,6 +4347,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3046,6 +4372,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3060,6 +4395,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3074,13 +4418,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3104,6 +4451,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3120,6 +4482,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3136,6 +4507,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3152,6 +4532,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3168,6 +4557,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3182,6 +4580,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3196,13 +4603,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3226,6 +4636,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3242,6 +4667,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3258,6 +4692,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3274,6 +4717,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3290,6 +4742,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3304,6 +4765,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3318,13 +4788,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3348,6 +4821,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3364,6 +4852,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3380,6 +4877,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3396,6 +4902,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3412,6 +4927,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3426,6 +4950,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3440,13 +4973,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3470,6 +5006,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3486,6 +5037,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3502,6 +5062,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3518,6 +5087,15 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3534,6 +5112,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3548,6 +5135,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3562,13 +5158,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3592,6 +5191,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3608,6 +5222,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3624,6 +5247,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3640,6 +5272,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3656,6 +5297,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3671,6 +5321,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3684,13 +5343,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3714,6 +5376,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3722,13 +5399,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3746,6 +5432,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3762,6 +5457,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3778,6 +5482,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3793,6 +5506,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3806,13 +5528,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3836,6 +5561,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3852,6 +5592,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3868,6 +5617,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3884,6 +5642,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3900,6 +5667,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3915,6 +5691,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3928,13 +5713,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3958,6 +5746,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3974,6 +5777,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3990,6 +5802,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4006,6 +5827,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4022,6 +5852,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4037,6 +5876,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4050,13 +5898,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4080,6 +5931,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4096,6 +5962,15 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4112,6 +5987,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4128,6 +6012,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4144,6 +6037,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4159,6 +6061,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4172,13 +6083,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4202,6 +6116,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4218,6 +6147,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4234,6 +6172,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4250,6 +6197,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4266,6 +6222,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4281,6 +6246,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4294,13 +6268,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4324,6 +6301,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4332,13 +6324,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4356,6 +6357,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4372,6 +6382,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4388,6 +6407,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4403,6 +6431,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4416,13 +6453,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4446,6 +6486,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4462,6 +6517,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4478,6 +6542,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4494,6 +6567,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4510,6 +6592,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4525,6 +6616,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4538,13 +6638,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4568,6 +6671,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4584,6 +6702,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4600,6 +6727,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4616,6 +6752,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4632,6 +6777,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4646,6 +6800,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4660,13 +6823,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4690,6 +6856,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4698,13 +6879,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4722,6 +6912,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4738,6 +6937,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4754,6 +6962,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4769,6 +6986,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4782,13 +7008,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4812,6 +7041,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4828,6 +7072,15 @@
       <c r="D2" t="n">
         <v>50</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4844,6 +7097,15 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4860,6 +7122,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4876,6 +7147,15 @@
       <c r="D5" t="n">
         <v>100</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4891,6 +7171,15 @@
       </c>
       <c r="D6" t="n">
         <v>-100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4904,15 +7193,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4946,6 +7240,31 @@
           <t>Baseline GCR (10회)</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (10회)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (10회)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4972,6 +7291,25 @@
           <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4980,22 +7318,41 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96.67</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>63.37</v>
+        <v>66.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 66.7, 100.0, 100.0, 100.0</t>
+          <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5024,6 +7381,25 @@
           <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5050,6 +7426,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5076,6 +7471,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5084,14 +7498,27 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>99.33</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>46.66</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>52.67</v>
-      </c>
+        <v>53.34</v>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5104,15 +7531,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5146,6 +7578,31 @@
           <t>Baseline GCR (10회)</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (10회)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (10회)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5172,6 +7629,25 @@
           <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5198,6 +7674,25 @@
           <t>33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5206,22 +7701,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>-85</v>
+        <v>-95</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0, 50.0, 0.0, 0.0, 50.0, 0.0, 0.0, 50.0, 0.0, 0.0</t>
+          <t>0.0, 50.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5232,22 +7746,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" t="n">
         <v>100</v>
       </c>
       <c r="D5" t="n">
-        <v>-20</v>
+        <v>-15</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0, 100.0, 100.0, 100.0, 100.0, 50.0, 100.0, 50.0, 50.0, 100.0</t>
+          <t>100.0, 50.0, 100.0, 50.0, 100.0, 100.0, 100.0, 50.0, 100.0, 100.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5276,6 +7809,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5284,14 +7836,27 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>72.34</v>
+        <v>71.34</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>76.66</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-4.32</v>
-      </c>
+        <v>-5.32</v>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5304,15 +7869,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5346,6 +7916,31 @@
           <t>Baseline GCR (10회)</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (10회)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (10회)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5372,6 +7967,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5398,6 +8012,25 @@
           <t>33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3, 33.3</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5424,6 +8057,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5450,6 +8102,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5476,6 +8147,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5492,6 +8182,19 @@
       <c r="D8" s="3" t="n">
         <v>13.34</v>
       </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5504,15 +8207,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5546,6 +8254,31 @@
           <t>Baseline GCR (10회)</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline 평균 Exec (%)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (10회)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (10회)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5554,22 +8287,41 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
         <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100.0, 100.0, 100.0, 100.0, 50.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
+          <t>100.0, 50.0, 100.0, 100.0, 50.0, 100.0, 50.0, 100.0, 50.0, 100.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0, 50.0</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5598,6 +8350,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5624,6 +8395,25 @@
           <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5650,6 +8440,25 @@
           <t>0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0</t>
         </is>
       </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5676,6 +8485,25 @@
           <t>100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0, 100.0</t>
         </is>
       </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -5684,14 +8512,27 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>50</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>29</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n"/>
+      <c r="K8" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5704,13 +8545,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5734,6 +8578,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5750,6 +8609,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5766,6 +8634,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5782,6 +8659,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5798,6 +8684,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5812,6 +8707,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5826,13 +8730,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5856,6 +8763,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5872,6 +8794,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5888,6 +8819,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5904,6 +8844,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5920,6 +8869,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5934,6 +8892,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5948,13 +8915,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5978,6 +8948,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5994,6 +8979,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6010,6 +9004,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6026,6 +9029,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6042,6 +9054,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6056,6 +9077,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6070,13 +9100,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6100,6 +9133,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6116,6 +9164,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6124,13 +9181,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
         <v>33.3</v>
       </c>
       <c r="D3" t="n">
-        <v>33.4</v>
+        <v>66.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -6148,6 +9214,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6164,6 +9239,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6178,6 +9262,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6192,13 +9285,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6222,6 +9318,21 @@
           <t>차이 (PG - BL)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Physical Guard Exec (%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Baseline Exec (%)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>차이 Exec (PG - BL)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6238,6 +9349,15 @@
       <c r="D2" t="n">
         <v>100</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6254,6 +9374,15 @@
       <c r="D3" t="n">
         <v>66.7</v>
       </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6270,6 +9399,15 @@
       <c r="D4" t="n">
         <v>100</v>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6286,6 +9424,15 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6300,6 +9447,15 @@
         <v>100</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0</v>
       </c>
     </row>
